--- a/estratégias.xlsx
+++ b/estratégias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.muniz\Claude\Projects\BI Tráfego Pago\Criativos\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1966F981-F78B-42BE-8B38-4ECC6000D4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595C11A8-D6AE-48C9-AF21-5FC862B5FB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D402DFE-FD87-4E21-968A-65E58F08E66C}"/>
   </bookViews>
@@ -1043,7 +1043,7 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2">
         <v>46209</v>
@@ -1081,7 +1081,7 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2">
         <v>46209</v>
@@ -1119,7 +1119,7 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2">
         <v>46209</v>
@@ -1157,7 +1157,7 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C17" s="2">
         <v>46209</v>
@@ -1195,7 +1195,7 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C18" s="2">
         <v>46209</v>

--- a/estratégias.xlsx
+++ b/estratégias.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.muniz\Claude\Projects\BI Tráfego Pago\Criativos\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595C11A8-D6AE-48C9-AF21-5FC862B5FB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FEE798-4943-4726-9DB3-1593938A0623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6D402DFE-FD87-4E21-968A-65E58F08E66C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D402DFE-FD87-4E21-968A-65E58F08E66C}"/>
   </bookViews>
   <sheets>
     <sheet name="Cidade Alegre" sheetId="1" r:id="rId1"/>
+    <sheet name="Nova Quinta" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="41">
   <si>
     <t>Tipo (feed/carrossel)</t>
   </si>
@@ -138,6 +139,30 @@
   </si>
   <si>
     <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Nova casa (lugar), Área residencial (imóveis), Condomínio (imóveis), Investimento imobiliário (investimento), Imóveis (indústria), Propriedade de imóveis (imóveis), Primeira casa (imóveis) ou Subsídio para compra da primeira casa (imóveis)</t>
+  </si>
+  <si>
+    <t>Semelhante (1%) - Análise de crédito | API Meta, Semelhante (1%) - Com Reserva | API Meta, Semelhante (1%) - Visita Realizada | API Meta, Conversores forms 30D</t>
+  </si>
+  <si>
+    <t>25-40</t>
+  </si>
+  <si>
+    <t>fmd-nova-quinta_segmentacao-interesses_marcas-de-luxo_pouso-form-nativo</t>
+  </si>
+  <si>
+    <t>fmd-nova-quinta_segmentacao-lookalike_analise-credito-visita-reserva_pouso-form-nativo</t>
+  </si>
+  <si>
+    <t>Ralph Lauren, Balenciaga (marca de moda), Land Rover (veículo), Viagem em primeira classe (negócios de viagem e turismo), iate clube (clubes e associações com base em interesses), Giorgio Armani, Calvin Klein (marca de moda), Porsche, Hermès (vestuário), Prada (marca de moda), BMW (veículos), Chanel (marca de moda), iatismo (barcos e embarcações), Iatismo, Audi (veículos), Lamborghini (veículos), Golfe (esporte), Bottega Veneta, Dolce &amp; Gabbana (marca de moda), Bentley, Armani (vestuário), Iate de luxo, Christian Dior, Cartier (joalheria), Barcos ou Veículo de luxo (veículos), Comportamentos: Viajantes internacionais frequentes</t>
+  </si>
+  <si>
+    <t>Ativado</t>
+  </si>
+  <si>
+    <t>NQ_Set_2026-01, NQ_Set_2026-02, NQ_Set_2026-03, NQ_Set_2026-04, NQ_Set_2026-05</t>
+  </si>
+  <si>
+    <t>CA-01, CA-02, CA-03, CA-04, CA-05</t>
   </si>
 </sst>
 </file>
@@ -527,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C175BC-2395-484C-81B8-8D65648F2DA1}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="61.21875" bestFit="1" customWidth="1"/>
@@ -611,7 +636,7 @@
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
@@ -622,13 +647,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2">
-        <v>46293</v>
+        <v>46209</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -643,13 +668,13 @@
         <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -660,13 +685,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="2">
-        <v>46293</v>
+        <v>46209</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -681,13 +706,13 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
         <v>24</v>
@@ -698,13 +723,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2">
-        <v>46293</v>
+        <v>46209</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -719,13 +744,13 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K5" t="s">
         <v>24</v>
@@ -736,13 +761,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>46293</v>
+        <v>46209</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -757,13 +782,13 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s">
         <v>24</v>
@@ -801,7 +826,7 @@
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
         <v>24</v>
@@ -815,7 +840,7 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2">
         <v>46209</v>
@@ -839,7 +864,7 @@
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
         <v>24</v>
@@ -850,10 +875,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2">
         <v>46209</v>
@@ -862,10 +887,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
         <v>20</v>
@@ -877,7 +902,7 @@
         <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
@@ -888,7 +913,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -900,10 +925,10 @@
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
         <v>20</v>
@@ -915,7 +940,7 @@
         <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K10" t="s">
         <v>24</v>
@@ -926,7 +951,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -938,10 +963,10 @@
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
         <v>20</v>
@@ -953,7 +978,7 @@
         <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K11" t="s">
         <v>24</v>
@@ -964,10 +989,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2">
         <v>46209</v>
@@ -976,10 +1001,10 @@
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
@@ -991,7 +1016,7 @@
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K12" t="s">
         <v>24</v>
@@ -1005,7 +1030,7 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C13" s="2">
         <v>46209</v>
@@ -1029,7 +1054,7 @@
         <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -1067,164 +1092,12 @@
         <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K14" t="s">
         <v>24</v>
       </c>
       <c r="L14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="2">
-        <v>46209</v>
-      </c>
-      <c r="D15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="2">
-        <v>46209</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" t="s">
-        <v>13</v>
-      </c>
-      <c r="K16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="2">
-        <v>46209</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" t="s">
-        <v>14</v>
-      </c>
-      <c r="K17" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="2">
-        <v>46209</v>
-      </c>
-      <c r="D18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1232,4 +1105,139 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884EA0F-91DC-43BE-AF44-A3A3AD18B40A}">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultColWidth="41.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="30.21875" customWidth="1"/>
+    <col min="5" max="5" width="35.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" customWidth="1"/>
+    <col min="8" max="8" width="27.6640625" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" customWidth="1"/>
+    <col min="10" max="10" width="27" customWidth="1"/>
+    <col min="11" max="11" width="24.21875" customWidth="1"/>
+    <col min="12" max="12" width="29.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/estratégias.xlsx
+++ b/estratégias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.muniz\Claude\Projects\BI Tráfego Pago\Criativos\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FEE798-4943-4726-9DB3-1593938A0623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE406A7-1CDD-4B6B-8FD3-71ED1FE4E245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D402DFE-FD87-4E21-968A-65E58F08E66C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6D402DFE-FD87-4E21-968A-65E58F08E66C}"/>
   </bookViews>
   <sheets>
     <sheet name="Cidade Alegre" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="44">
   <si>
     <t>Tipo (feed/carrossel)</t>
   </si>
@@ -159,10 +159,19 @@
     <t>Ativado</t>
   </si>
   <si>
-    <t>NQ_Set_2026-01, NQ_Set_2026-02, NQ_Set_2026-03, NQ_Set_2026-04, NQ_Set_2026-05</t>
-  </si>
-  <si>
-    <t>CA-01, CA-02, CA-03, CA-04, CA-05</t>
+    <t>Soma</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Soma Acumulada</t>
+  </si>
+  <si>
+    <t>Contagem</t>
+  </si>
+  <si>
+    <t>NQ_Set_2026-01.png, NQ_Set_2026-02.png, NQ_Set_2026-03.png, NQ_Set_2026-04.png, NQ_Set_2026-05.png</t>
   </si>
 </sst>
 </file>
@@ -552,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C175BC-2395-484C-81B8-8D65648F2DA1}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="61.21875" bestFit="1" customWidth="1"/>
@@ -636,7 +645,7 @@
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
@@ -647,13 +656,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2">
-        <v>46209</v>
+        <v>46293</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -668,13 +677,13 @@
         <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>
@@ -685,13 +694,13 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="2">
-        <v>46209</v>
+        <v>46293</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -706,13 +715,13 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" t="s">
         <v>24</v>
@@ -723,13 +732,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2">
-        <v>46209</v>
+        <v>46293</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -744,13 +753,13 @@
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
         <v>24</v>
@@ -761,13 +770,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2">
-        <v>46209</v>
+        <v>46293</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -782,13 +791,13 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
         <v>24</v>
@@ -826,7 +835,7 @@
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K7" t="s">
         <v>24</v>
@@ -840,7 +849,7 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2">
         <v>46209</v>
@@ -864,7 +873,7 @@
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
         <v>24</v>
@@ -875,10 +884,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C9" s="2">
         <v>46209</v>
@@ -887,10 +896,10 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
         <v>20</v>
@@ -902,7 +911,7 @@
         <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
@@ -913,7 +922,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -925,10 +934,10 @@
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G10" t="s">
         <v>20</v>
@@ -940,7 +949,7 @@
         <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K10" t="s">
         <v>24</v>
@@ -951,7 +960,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -963,10 +972,10 @@
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
         <v>20</v>
@@ -978,7 +987,7 @@
         <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K11" t="s">
         <v>24</v>
@@ -989,10 +998,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2">
         <v>46209</v>
@@ -1001,10 +1010,10 @@
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
@@ -1016,7 +1025,7 @@
         <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K12" t="s">
         <v>24</v>
@@ -1030,7 +1039,7 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2">
         <v>46209</v>
@@ -1054,7 +1063,7 @@
         <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -1092,12 +1101,164 @@
         <v>18</v>
       </c>
       <c r="J14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46209</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46209</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2">
+        <v>46209</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46209</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s">
         <v>15</v>
       </c>
-      <c r="K14" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="K18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1190,7 +1351,7 @@
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
@@ -1228,7 +1389,7 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
         <v>24</v>

--- a/estratégias.xlsx
+++ b/estratégias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.muniz\Claude\Projects\BI Tráfego Pago\Criativos\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE406A7-1CDD-4B6B-8FD3-71ED1FE4E245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C33F7D1-22BA-467B-A5F2-7D7808E4524F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6D402DFE-FD87-4E21-968A-65E58F08E66C}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="48">
   <si>
     <t>Tipo (feed/carrossel)</t>
   </si>
@@ -171,7 +171,19 @@
     <t>Contagem</t>
   </si>
   <si>
-    <t>NQ_Set_2026-01.png, NQ_Set_2026-02.png, NQ_Set_2026-03.png, NQ_Set_2026-04.png, NQ_Set_2026-05.png</t>
+    <t>NQ_Set_2026-01.png</t>
+  </si>
+  <si>
+    <t>NQ_Set_2026-02.png</t>
+  </si>
+  <si>
+    <t>NQ_Set_2026-03.png</t>
+  </si>
+  <si>
+    <t>NQ_Set_2026-04.png</t>
+  </si>
+  <si>
+    <t>NQ_Set_2026-05.png</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884EA0F-91DC-43BE-AF44-A3A3AD18B40A}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="41.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="21" customWidth="1"/>
@@ -1362,7 +1374,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -1377,7 +1389,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
         <v>34</v>
@@ -1389,12 +1401,316 @@
         <v>18</v>
       </c>
       <c r="J3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
         <v>43</v>
       </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="K7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" t="s">
         <v>38</v>
       </c>
     </row>

--- a/estratégias.xlsx
+++ b/estratégias.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.muniz\Claude\Projects\BI Tráfego Pago\Criativos\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.muniz\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98153A92-0D97-4503-BB3D-273A2936E22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5323F24A-2E0F-4317-90EE-118F50DD426C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6D402DFE-FD87-4E21-968A-65E58F08E66C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B48E7D59-4599-45D1-96C6-7F892DAA9022}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cidade Alegre" sheetId="1" r:id="rId1"/>
-    <sheet name="Nova Quinta" sheetId="2" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$L$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,133 +42,155 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="40">
-  <si>
-    <t>Tipo (feed/carrossel)</t>
-  </si>
-  <si>
-    <t>Data Início</t>
-  </si>
-  <si>
-    <t>Data Fim</t>
-  </si>
-  <si>
-    <t>Localização</t>
-  </si>
-  <si>
-    <t>Público</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
+  <si>
+    <t>Empreendimentos</t>
+  </si>
+  <si>
+    <t>Cidade Alegre</t>
+  </si>
+  <si>
+    <t>Nova Quinta</t>
+  </si>
+  <si>
+    <t>Jardim dos Ipês</t>
+  </si>
+  <si>
+    <t>Piemonte</t>
+  </si>
+  <si>
+    <t>Altos da Serra</t>
+  </si>
+  <si>
+    <t>Monte Verde</t>
+  </si>
+  <si>
+    <t>Parque Aviação</t>
+  </si>
+  <si>
+    <t>Raízes Di Verona</t>
+  </si>
+  <si>
+    <t>Orquídeas</t>
+  </si>
+  <si>
+    <t>Jardim Corumbataí</t>
+  </si>
+  <si>
+    <t>Situação de campanhas</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>Finalizado</t>
+  </si>
+  <si>
+    <t>Cidade do empreendimento</t>
+  </si>
+  <si>
+    <t>Renda familiar</t>
+  </si>
+  <si>
+    <t>Localizações patrocinados</t>
+  </si>
+  <si>
+    <t>Bauru</t>
+  </si>
+  <si>
+    <t>Jaú</t>
+  </si>
+  <si>
+    <t>Botucatu</t>
+  </si>
+  <si>
+    <t>São Pedro</t>
+  </si>
+  <si>
+    <t>Pirassununga</t>
+  </si>
+  <si>
+    <t>São José do Rio Preto</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>Rio Claro</t>
+  </si>
+  <si>
+    <t>Plataformas de TP</t>
+  </si>
+  <si>
+    <t>Tipo de Campanhas</t>
   </si>
   <si>
     <t>Faixa Etária</t>
   </si>
   <si>
-    <t>Tipo Campanha</t>
-  </si>
-  <si>
-    <t>Plataforma</t>
-  </si>
-  <si>
-    <t>Nome Imagem</t>
-  </si>
-  <si>
-    <t>feed</t>
-  </si>
-  <si>
-    <t>Bauru</t>
-  </si>
-  <si>
-    <t>Campanha</t>
-  </si>
-  <si>
-    <t>WhatsApp</t>
+    <t>Público-Alvo</t>
+  </si>
+  <si>
+    <t>Público Advantage+</t>
+  </si>
+  <si>
+    <t>Posicionamentos  Advantage+</t>
+  </si>
+  <si>
+    <t>Tipos de anúncio</t>
   </si>
   <si>
     <t>Meta</t>
   </si>
   <si>
-    <t>fmd-cidade-alegre_segmentacao-interesses-imoveis_pouso-whatsapp-v2</t>
+    <t>WhatsApp e Cadastro</t>
+  </si>
+  <si>
+    <t>Feed, Stories</t>
   </si>
   <si>
     <t>20-45</t>
   </si>
   <si>
-    <t xml:space="preserve"> Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Nova casa (lugar), Lar (casa e jardim), Investimento imobiliário (investimento), Imóveis (indústria), Propriedade de imóveis (imóveis) ou Primeira casa (imóveis)</t>
-  </si>
-  <si>
-    <t>Sem data de término</t>
-  </si>
-  <si>
-    <t>Público Advantage+</t>
-  </si>
-  <si>
     <t>Desativado</t>
   </si>
   <si>
-    <t>Posicionamentos  Advantage+</t>
-  </si>
-  <si>
-    <t>fmd-cidade-alegre_segmentacao-interesses_imoveis_pouso-form-nativo</t>
-  </si>
-  <si>
-    <t>Cadastro</t>
-  </si>
-  <si>
-    <t>fmd-cidade-alegre_segmentacao-interesses_geo-imoveis_pouso-form-nativo</t>
-  </si>
-  <si>
-    <t>carrossel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrossel-CA-01.png, Carrossel-CA-02.png, Carrossel-CA-03.png, Carrossel-CA-04.png, Carrossel-CA-05.png, </t>
-  </si>
-  <si>
-    <t>Araújo Leite 2_85 Formotos (+2 km), Latitude -22,31 Longitude -49,12 Bauru (+2 km), Latitude -22,36 Longitude -49,10 Bauru (+2 km), Latitude -22,36 Longitude -49,05 Bauru (+2 km), Latitude -22,37 Longitude -49,09 Bauru (+2 km) São Paulo (state)</t>
-  </si>
-  <si>
     <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Nova casa (lugar), Área residencial (imóveis), Condomínio (imóveis), Investimento imobiliário (investimento), Imóveis (indústria), Propriedade de imóveis (imóveis), Primeira casa (imóveis) ou Subsídio para compra da primeira casa (imóveis)</t>
   </si>
   <si>
+    <t>Parque Primavera, Jardim Eldorado, Parque Jaraguá, Vila Nipônica, Jardim Vitória, Jardim Terra Branca, Jardim Solange, Vila São Francisco, Parque Residencial Granja Cecília, Jardim América, Vila Aviação B, Parque Residencial Samambaia, Oarqye São Geraldo, Jardim Araruna, Vila Camargo, Vila Cardia, e +2KM de cada bairro</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Nova casa (lugar), Lar (casa e jardim), Investimento imobiliário (investimento), Imóveis (indústria), Propriedade de imóveis (imóveis) ou Primeira casa (imóveis)</t>
+  </si>
+  <si>
     <t>Semelhante (1%) - Análise de crédito | API Meta, Semelhante (1%) - Com Reserva | API Meta, Semelhante (1%) - Visita Realizada | API Meta, Conversores forms 30D</t>
   </si>
   <si>
+    <t>Ralph Lauren, Balenciaga (marca de moda), Land Rover (veículo), Viagem em primeira classe (negócios de viagem e turismo), iate clube (clubes e associações com base em interesses), Giorgio Armani, Calvin Klein (marca de moda), Porsche, Hermès (vestuário), Prada (marca de moda), BMW (veículos), Chanel (marca de moda), iatismo (barcos e embarcações), Iatismo, Audi (veículos), Lamborghini (veículos), Golfe (esporte), Bottega Veneta, Dolce &amp; Gabbana (marca de moda), Bentley, Armani (vestuário), Iate de luxo, Christian Dior, Cartier (joalheria), Barcos ou Veículo de luxo (veículos), Comportamentos: Viajantes internacionais frequentes</t>
+  </si>
+  <si>
+    <t>Ativado</t>
+  </si>
+  <si>
     <t>25-40</t>
-  </si>
-  <si>
-    <t>fmd-nova-quinta_segmentacao-interesses_marcas-de-luxo_pouso-form-nativo</t>
-  </si>
-  <si>
-    <t>fmd-nova-quinta_segmentacao-lookalike_analise-credito-visita-reserva_pouso-form-nativo</t>
-  </si>
-  <si>
-    <t>Ralph Lauren, Balenciaga (marca de moda), Land Rover (veículo), Viagem em primeira classe (negócios de viagem e turismo), iate clube (clubes e associações com base em interesses), Giorgio Armani, Calvin Klein (marca de moda), Porsche, Hermès (vestuário), Prada (marca de moda), BMW (veículos), Chanel (marca de moda), iatismo (barcos e embarcações), Iatismo, Audi (veículos), Lamborghini (veículos), Golfe (esporte), Bottega Veneta, Dolce &amp; Gabbana (marca de moda), Bentley, Armani (vestuário), Iate de luxo, Christian Dior, Cartier (joalheria), Barcos ou Veículo de luxo (veículos), Comportamentos: Viajantes internacionais frequentes</t>
-  </si>
-  <si>
-    <t>Ativado</t>
-  </si>
-  <si>
-    <t>Soma</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Soma Acumulada</t>
-  </si>
-  <si>
-    <t>Contagem</t>
-  </si>
-  <si>
-    <t>NQ_Set_2026-01.png, NQ_Set_2026-02.png, NQ_Set_2026-03.png, NQ_Set_2026-04.png, NQ_Set_2026-05.png</t>
-  </si>
-  <si>
-    <t>CA-01.png, CA-02.png, CA-03.png, CA-04.png, CA-05.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,12 +202,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -206,17 +224,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -548,389 +580,318 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C175BC-2395-484C-81B8-8D65648F2DA1}">
-  <dimension ref="A1:L6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B7E582-FFA2-4C3F-A634-F5CED051AC4F}">
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.88671875" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="17.109375" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.77734375" customWidth="1"/>
+    <col min="6" max="6" width="24.5546875" customWidth="1"/>
+    <col min="7" max="8" width="20.5546875" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" customWidth="1"/>
+    <col min="10" max="10" width="19.77734375" customWidth="1"/>
+    <col min="11" max="11" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46293</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="5">
+        <v>3200</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="J2" t="s">
         <v>39</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46209</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
+      <c r="A3" s="6"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="4"/>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46209</v>
-      </c>
-      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5">
+        <v>6500</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="2">
-        <v>46209</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="4"/>
+      <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3200</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>15000</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3500</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2900</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2500</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1">
+        <v>4000</v>
+      </c>
+      <c r="D12" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2">
-        <v>46209</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="J6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>19</v>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4700</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D884EA0F-91DC-43BE-AF44-A3A3AD18B40A}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="41.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="30.21875" customWidth="1"/>
-    <col min="5" max="5" width="35.44140625" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" customWidth="1"/>
-    <col min="8" max="8" width="27.6640625" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" customWidth="1"/>
-    <col min="10" max="10" width="27" customWidth="1"/>
-    <col min="11" max="11" width="24.21875" customWidth="1"/>
-    <col min="12" max="12" width="29.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2">
-        <v>46266</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46266</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:L1" xr:uid="{E0B7E582-FFA2-4C3F-A634-F5CED051AC4F}"/>
+  <mergeCells count="6">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/estratégias.xlsx
+++ b/estratégias.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5323F24A-2E0F-4317-90EE-118F50DD426C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B48E7D59-4599-45D1-96C6-7F892DAA9022}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B48E7D59-4599-45D1-96C6-7F892DAA9022}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -238,13 +238,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -636,16 +636,16 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="6">
         <v>3200</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
@@ -674,10 +674,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="4"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="5"/>
       <c r="E3" t="s">
         <v>38</v>
       </c>
@@ -707,13 +707,13 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="6">
         <v>6500</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E4" t="s">
@@ -742,9 +742,9 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
       <c r="E5" t="s">
         <v>17</v>
       </c>

--- a/estratégias.xlsx
+++ b/estratégias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.muniz\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5323F24A-2E0F-4317-90EE-118F50DD426C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2928BAC-B128-47E1-87E2-459B5203B1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B48E7D59-4599-45D1-96C6-7F892DAA9022}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="62">
   <si>
     <t>Empreendimentos</t>
   </si>
@@ -174,14 +174,69 @@
   </si>
   <si>
     <t>25-40</t>
+  </si>
+  <si>
+    <t>25-45</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Comprador de primeiro imóvel (imóveis), Nova casa (lugar), Investimento imobiliário (investimento), Propriedade de imóveis (imóveis), Primeira casa (imóveis) ou Subsídio para compra da primeira casa (imóveis)</t>
+  </si>
+  <si>
+    <t>Abriam forms 30D, Abriaram forms 60D, Abril/Não enviaram forms 30D, Abril/Não enviaram forms 60D</t>
+  </si>
+  <si>
+    <t>WhatsApp</t>
+  </si>
+  <si>
+    <t>Cuiabá, Várzea Grande, Nossa Senhora do Livramento, Santo Antônio de Leverger, Chapada dos Guimarães</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alphaville Cuiabá +1km, Alphaville Cuiabá II + 2km, Avenida Beira Rio, Avenida das Florais, Jardim Mariana, Jardim Rosa +2km </t>
+  </si>
+  <si>
+    <t>Cadastro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semelhante (1%) Análise de crédito | API Meta, Semelhante (1%)  Com reserva | API Meta, Semelhante (1%)  Venda realizada | API Meta, Semelhante (1%)  Visita realizada | API Meta, </t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Investimento (negócios e finanças), Nova casa (lugar), Investimento imobiliário (investimento), Primeira casa (imóveis) ou Subsídio para compra da primeira casa (imóveis)</t>
+  </si>
+  <si>
+    <t>Feed, Stories, Motion</t>
+  </si>
+  <si>
+    <t>Cuiabá + 15km</t>
+  </si>
+  <si>
+    <t>Cuiabá +15 km</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Lar (casa e jardim), Área residencial (imóveis), Imóveis (indústria) ou Primeira casa (imóveis)</t>
+  </si>
+  <si>
+    <t>Zona Norte por completo</t>
+  </si>
+  <si>
+    <t>Setvalley + 3km, Bosque da Felicidade + 2km, São Deocleciano + 1km, Jardim Maria Candida + 2km, Residencial Palestra + 2km, Cidade Jardim + 2km, Vila Toninho + 1km</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Comprador de primeiro imóvel (imóveis), Área residencial (imóveis), Primeira casa (imóveis) ou Subsídio para compra da primeira casa (imóveis)</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Condomínio fechado (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Nova casa (lugar), Área residencial (imóveis), Condomínio (imóveis), Imóveis (indústria), Propriedade de imóveis (imóveis), Primeira casa (imóveis), Subsídio para compra da primeira casa (imóveis) ou Imóveis residenciais (imóveis), Acontecimento: Noivaram recentemente (1 ano)</t>
+  </si>
+  <si>
+    <t>Rio Preto, Bady Bassitt, Guapiaçu, Mirassol</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -228,9 +283,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -240,10 +294,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -581,12 +639,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B7E582-FFA2-4C3F-A634-F5CED051AC4F}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
     <col min="2" max="2" width="21.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.77734375" customWidth="1"/>
     <col min="6" max="6" width="24.5546875" customWidth="1"/>
@@ -597,55 +655,55 @@
     <col min="12" max="12" width="27.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>3200</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
@@ -674,10 +732,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="5"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="6"/>
       <c r="E3" t="s">
         <v>38</v>
       </c>
@@ -707,13 +765,13 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>6500</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E4" t="s">
@@ -742,9 +800,9 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="5"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="6"/>
       <c r="E5" t="s">
         <v>17</v>
       </c>
@@ -777,7 +835,7 @@
       <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="5">
         <v>3200</v>
       </c>
       <c r="D6" t="s">
@@ -791,7 +849,7 @@
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="5">
         <v>15000</v>
       </c>
       <c r="D7" t="s">
@@ -805,7 +863,7 @@
       <c r="B8" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="5">
         <v>3500</v>
       </c>
       <c r="D8" t="s">
@@ -819,7 +877,7 @@
       <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="5">
         <v>2900</v>
       </c>
       <c r="D9" t="s">
@@ -833,7 +891,7 @@
       <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="5">
         <v>2500</v>
       </c>
       <c r="D10" t="s">
@@ -844,47 +902,334 @@
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="7">
         <v>3100</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
+      <c r="E11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="6"/>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" t="s">
+        <v>59</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="6"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="6"/>
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C14" s="7">
         <v>4000</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="6"/>
+      <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" t="s">
+        <v>53</v>
+      </c>
+      <c r="I15" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="6"/>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" t="s">
+        <v>53</v>
+      </c>
+      <c r="I16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" t="s">
+        <v>42</v>
+      </c>
+      <c r="L16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="6"/>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" t="s">
+        <v>42</v>
+      </c>
+      <c r="L17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="6"/>
+      <c r="E18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="6"/>
+      <c r="E19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" t="s">
+        <v>42</v>
+      </c>
+      <c r="L19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="6"/>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" t="s">
+        <v>52</v>
+      </c>
+      <c r="K20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B21" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C21" s="5">
         <v>4700</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D21" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L1" xr:uid="{E0B7E582-FFA2-4C3F-A634-F5CED051AC4F}"/>
-  <mergeCells count="6">
+  <mergeCells count="13">
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="B14:B20"/>
+    <mergeCell ref="C14:C20"/>
+    <mergeCell ref="D14:D20"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="B11:B13"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="B2:B3"/>

--- a/estratégias.xlsx
+++ b/estratégias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.muniz\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2928BAC-B128-47E1-87E2-459B5203B1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB27526-7770-42F5-A189-3345222E28B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B48E7D59-4599-45D1-96C6-7F892DAA9022}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="85">
   <si>
     <t>Empreendimentos</t>
   </si>
@@ -158,9 +158,6 @@
     <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Nova casa (lugar), Área residencial (imóveis), Condomínio (imóveis), Investimento imobiliário (investimento), Imóveis (indústria), Propriedade de imóveis (imóveis), Primeira casa (imóveis) ou Subsídio para compra da primeira casa (imóveis)</t>
   </si>
   <si>
-    <t>Parque Primavera, Jardim Eldorado, Parque Jaraguá, Vila Nipônica, Jardim Vitória, Jardim Terra Branca, Jardim Solange, Vila São Francisco, Parque Residencial Granja Cecília, Jardim América, Vila Aviação B, Parque Residencial Samambaia, Oarqye São Geraldo, Jardim Araruna, Vila Camargo, Vila Cardia, e +2KM de cada bairro</t>
-  </si>
-  <si>
     <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Nova casa (lugar), Lar (casa e jardim), Investimento imobiliário (investimento), Imóveis (indústria), Propriedade de imóveis (imóveis) ou Primeira casa (imóveis)</t>
   </si>
   <si>
@@ -228,6 +225,78 @@
   </si>
   <si>
     <t>Rio Preto, Bady Bassitt, Guapiaçu, Mirassol</t>
+  </si>
+  <si>
+    <t>20-40</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Condomínio fechado (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Área residencial (imóveis), Condomínio (imóveis), Imóveis (indústria), Propriedade de imóveis (imóveis) ou Primeira casa (imóveis)</t>
+  </si>
+  <si>
+    <t>Semelhante (1%) Lista de leads análise de crédito + reserva | API Meta. Casa (imóveis) ou Comprador de primeiro imóvel (imóveis)</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Condomínio fechado (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Nova casa (lugar), Lar (casa e jardim), Área residencial (imóveis), Condomínio (imóveis), Investimento imobiliário (investimento), Imóveis (indústria), Propriedade de imóveis (imóveis), Primeira casa (imóveis) ou Subsídio para compra da primeira casa (imóveis)</t>
+  </si>
+  <si>
+    <t>Parque Primavera, Jardim Eldorado, Parque Jaraguá, Vila Nipônica, Jardim Vitória, Jardim Terra Branca, Jardim Solange, Vila São Francisco, Parque Residencial Granja Cecília, Jardim América, Vila Aviação B, Parque Residencial Samambaia, Parque São Geraldo, Jardim Araruna, Vila Camargo, Vila Cardia, e +2KM de cada bairro</t>
+  </si>
+  <si>
+    <t>Jaú + 15km</t>
+  </si>
+  <si>
+    <t>São Pedro + 2km</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Condomínio fechado (imóveis), Apartamento (imóveis), Investimento (negócios e finanças), Nova casa (lugar), Lar (casa e jardim), Área residencial (imóveis), Condomínio (imóveis), Investimento imobiliário (investimento), Imóveis (indústria), Investidor (investimento) ou Propriedade de imóveis (imóveis)</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Nova casa (lugar), Área residencial (imóveis), Imóveis (indústria), Propriedade de imóveis (imóveis) ou Primeira casa (imóveis)</t>
+  </si>
+  <si>
+    <t>São Pedro + 10km</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Nova casa (lugar), Lar (casa e jardim), Área residencial (imóveis), Condomínio (imóveis), Investimento imobiliário (investimento), Imóveis (indústria), Propriedade de imóveis (imóveis), Primeira casa (imóveis) ou Imóveis residenciais (imóveis)</t>
+  </si>
+  <si>
+    <t>Botucatu +17 km</t>
+  </si>
+  <si>
+    <t>Alcance</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Nova casa (lugar), Área residencial (imóveis), Investimento imobiliário (investimento), Imóveis (indústria) ou Propriedade de imóveis (imóveis)</t>
+  </si>
+  <si>
+    <t>Blowpet Transformacoes Plasticas (+2 km), Inbrasp - Indústria Brasileira De Plásticos (+2 km), Gruppi Concreto (+2 km), Embraer Botucatu (+2 km), Rodovia Marechal Rondon - 254km (+2 km), Sesi Botucatu (+2 km), Shopping Park Botucatu (+2 km), Rua José Lapenna, 231, Botucatu (+2 km), Rodovia Marechal Rondon, Botucatu (+1 km), Rua Jayme Contessotte, 338, Botucatu (+3 km) São Paulo (state)</t>
+  </si>
+  <si>
+    <t>25-60</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Nova casa (lugar), Lar (casa e jardim), Área residencial (imóveis), Investimento imobiliário (investimento), Imóveis (indústria), Propriedade de imóveis (imóveis), Primeira casa (imóveis) ou Subsídio para compra da primeira casa (imóveis)</t>
+  </si>
+  <si>
+    <t>Botucatu + 7km</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Apartamento (imóveis), Comprador de primeiro imóvel (imóveis), Casa unifamiliar (imóveis), Nova casa (lugar), Lar (casa e jardim), Área residencial (imóveis), Investimento imobiliário (investimento), Imóveis (indústria) ou Primeira casa (imóveis)</t>
+  </si>
+  <si>
+    <t>Botucatu +20km</t>
+  </si>
+  <si>
+    <t>Semelhante (BR,1%) - Base Ecovilla Fev26</t>
+  </si>
+  <si>
+    <t>25-50</t>
+  </si>
+  <si>
+    <t>Semelhante (1%) - [FMD] Venda realizada | API Meta, Semelhante (1%) - [FMD] Visita realizada | API Meta, Semelhante (1%) - [FMD] Com reserva | API Meta, Semelhante (1%) - [FMD] Análise de crédito | API Meta, Semelhante (1%) - [FMD] Visita agendada | API Meta, Semelhante (1%) - ECOVITA | LISTA DE LEADS ANALISE CREDITO + RESERVA</t>
+  </si>
+  <si>
+    <t>Casa (imóveis), Comprador de primeiro imóvel (imóveis), Serviços financeiros (negócios e finanças), Crédito (finanças), Aluguel (imóveis), Casa unifamiliar (imóveis), Nova casa (lugar), Lar (casa e jardim), Área residencial (imóveis), Condomínio (imóveis), Investimento imobiliário (investimento), Imóveis (indústria), Primeira casa (imóveis), Linha de crédito (crédito e empréstimos), Subsídio para compra da primeira casa (imóveis) ou Serviços e organizações de crédito (crédito e empréstimo)</t>
   </si>
 </sst>
 </file>
@@ -283,7 +352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -301,8 +370,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -639,10 +714,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B7E582-FFA2-4C3F-A634-F5CED051AC4F}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="21.33203125" customWidth="1"/>
     <col min="3" max="3" width="20.109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="30.5546875" bestFit="1" customWidth="1"/>
@@ -656,7 +731,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -694,16 +769,16 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="8">
         <v>3200</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
@@ -722,7 +797,7 @@
         <v>35</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K2" t="s">
         <v>36</v>
@@ -732,12 +807,12 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="6"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="7"/>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
         <v>32</v>
@@ -762,16 +837,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="8">
         <v>6500</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E4" t="s">
@@ -787,22 +862,23 @@
         <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K4" t="s">
         <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="6"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="6"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="7"/>
       <c r="E5" t="s">
         <v>17</v>
       </c>
@@ -816,426 +892,815 @@
         <v>34</v>
       </c>
       <c r="I5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="8">
+        <v>3200</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="7"/>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="7"/>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5">
+        <v>15000</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="8">
+        <v>3500</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
         <v>43</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="7"/>
+      <c r="E11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="7"/>
+      <c r="E12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="7"/>
+      <c r="E13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="7"/>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" t="s">
         <v>41</v>
       </c>
-      <c r="K5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="7"/>
+      <c r="E15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5">
-        <v>3200</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="5">
-        <v>15000</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="5">
-        <v>3500</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C16" s="8">
         <v>2900</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D16" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2500</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="7">
-        <v>3100</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" t="s">
-        <v>56</v>
-      </c>
-      <c r="K11" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="6"/>
-      <c r="E12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" t="s">
-        <v>59</v>
-      </c>
-      <c r="K12" t="s">
-        <v>36</v>
-      </c>
-      <c r="L12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="6"/>
-      <c r="E13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>4000</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" t="s">
-        <v>45</v>
-      </c>
-      <c r="K14" t="s">
-        <v>42</v>
-      </c>
-      <c r="L14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="6"/>
-      <c r="E15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" t="s">
-        <v>53</v>
-      </c>
-      <c r="I15" t="s">
-        <v>44</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
         <v>46</v>
       </c>
-      <c r="K15" t="s">
-        <v>36</v>
-      </c>
-      <c r="L15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="6"/>
-      <c r="E16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" t="s">
-        <v>47</v>
-      </c>
       <c r="H16" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
         <v>35</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="K16" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L16" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="6"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="7"/>
       <c r="E17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
         <v>49</v>
       </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>47</v>
-      </c>
       <c r="H17" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="I17" t="s">
         <v>35</v>
       </c>
       <c r="J17" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="K17" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L17" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="6"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="7"/>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
         <v>32</v>
       </c>
       <c r="G18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H18" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
         <v>35</v>
       </c>
       <c r="J18" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K18" t="s">
         <v>36</v>
       </c>
       <c r="L18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="6"/>
-      <c r="E19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" t="s">
-        <v>53</v>
-      </c>
-      <c r="I19" t="s">
-        <v>35</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="5">
+        <v>2500</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="8">
+        <v>3100</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" t="s">
         <v>52</v>
-      </c>
-      <c r="K19" t="s">
-        <v>42</v>
-      </c>
-      <c r="L19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="6"/>
-      <c r="E20" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" t="s">
-        <v>53</v>
       </c>
       <c r="I20" t="s">
         <v>35</v>
       </c>
       <c r="J20" t="s">
+        <v>55</v>
+      </c>
+      <c r="K20" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="7"/>
+      <c r="E21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" t="s">
         <v>52</v>
       </c>
-      <c r="K20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="I21" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="7"/>
+      <c r="E22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K22" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="8">
+        <v>4000</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23" t="s">
+        <v>44</v>
+      </c>
+      <c r="K23" t="s">
+        <v>41</v>
+      </c>
+      <c r="L23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="7"/>
+      <c r="E24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24" t="s">
+        <v>45</v>
+      </c>
+      <c r="K24" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="7"/>
+      <c r="E25" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" t="s">
+        <v>44</v>
+      </c>
+      <c r="K25" t="s">
+        <v>41</v>
+      </c>
+      <c r="L25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="7"/>
+      <c r="E26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" t="s">
+        <v>44</v>
+      </c>
+      <c r="K26" t="s">
+        <v>41</v>
+      </c>
+      <c r="L26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="7"/>
+      <c r="E27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" t="s">
+        <v>50</v>
+      </c>
+      <c r="K27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L27" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="7"/>
+      <c r="E28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" t="s">
+        <v>51</v>
+      </c>
+      <c r="K28" t="s">
+        <v>41</v>
+      </c>
+      <c r="L28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="7"/>
+      <c r="E29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" t="s">
+        <v>51</v>
+      </c>
+      <c r="K29" t="s">
+        <v>36</v>
+      </c>
+      <c r="L29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B30" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C30" s="5">
         <v>4700</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D30" s="9" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L1" xr:uid="{E0B7E582-FFA2-4C3F-A634-F5CED051AC4F}"/>
-  <mergeCells count="13">
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="B14:B20"/>
-    <mergeCell ref="C14:C20"/>
-    <mergeCell ref="D14:D20"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="B11:B13"/>
+  <mergeCells count="28">
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="B10:B15"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="B23:B29"/>
+    <mergeCell ref="C23:C29"/>
+    <mergeCell ref="D23:D29"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="B20:B22"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/estratégias.xlsx
+++ b/estratégias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matheus.muniz\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB27526-7770-42F5-A189-3345222E28B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78915BB7-5DB1-4104-95FF-49761CE5F9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B48E7D59-4599-45D1-96C6-7F892DAA9022}"/>
   </bookViews>
@@ -303,9 +303,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="[$R$-416]\ #,##0.00;[Red][$R$-416]\ #,##0.00"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -366,17 +367,19 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -719,7 +722,7 @@
   <cols>
     <col min="1" max="1" width="24.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="21.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="9" customWidth="1"/>
     <col min="4" max="4" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.77734375" customWidth="1"/>
     <col min="6" max="6" width="24.5546875" customWidth="1"/>
@@ -769,16 +772,16 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="8">
         <v>3200</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
@@ -807,10 +810,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="7"/>
+      <c r="D3" s="6"/>
       <c r="E3" t="s">
         <v>65</v>
       </c>
@@ -837,16 +840,16 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="8">
         <v>6500</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E4" t="s">
@@ -875,10 +878,10 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="7"/>
+      <c r="D5" s="6"/>
       <c r="E5" t="s">
         <v>17</v>
       </c>
@@ -905,16 +908,16 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="8">
         <v>3200</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E6" t="s">
@@ -943,10 +946,10 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="7"/>
+      <c r="D7" s="6"/>
       <c r="E7" t="s">
         <v>18</v>
       </c>
@@ -973,10 +976,10 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="7"/>
+      <c r="D8" s="6"/>
       <c r="E8" t="s">
         <v>18</v>
       </c>
@@ -1003,16 +1006,16 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="9">
         <v>15000</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E9" t="s">
@@ -1041,16 +1044,16 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="8">
         <v>3500</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E10" t="s">
@@ -1079,10 +1082,10 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="7"/>
+      <c r="D11" s="6"/>
       <c r="E11" t="s">
         <v>75</v>
       </c>
@@ -1109,10 +1112,10 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="8"/>
-      <c r="D12" s="7"/>
+      <c r="D12" s="6"/>
       <c r="E12" t="s">
         <v>78</v>
       </c>
@@ -1139,10 +1142,10 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="7"/>
+      <c r="D13" s="6"/>
       <c r="E13" t="s">
         <v>80</v>
       </c>
@@ -1169,10 +1172,10 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="6"/>
       <c r="E14" t="s">
         <v>19</v>
       </c>
@@ -1199,10 +1202,10 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="7"/>
+      <c r="D15" s="6"/>
       <c r="E15" t="s">
         <v>72</v>
       </c>
@@ -1229,16 +1232,16 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="8">
         <v>2900</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>20</v>
       </c>
       <c r="E16" t="s">
@@ -1267,10 +1270,10 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="6"/>
       <c r="E17" t="s">
         <v>70</v>
       </c>
@@ -1297,10 +1300,10 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="6"/>
       <c r="E18" t="s">
         <v>70</v>
       </c>
@@ -1327,30 +1330,30 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="9">
         <v>2500</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="8">
         <v>3100</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E20" t="s">
@@ -1379,10 +1382,10 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="7"/>
+      <c r="D21" s="6"/>
       <c r="E21" t="s">
         <v>57</v>
       </c>
@@ -1409,10 +1412,10 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="6"/>
       <c r="E22" t="s">
         <v>60</v>
       </c>
@@ -1439,16 +1442,16 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="8">
         <v>4000</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="E23" t="s">
@@ -1477,10 +1480,10 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="7"/>
+      <c r="D24" s="6"/>
       <c r="E24" t="s">
         <v>54</v>
       </c>
@@ -1507,10 +1510,10 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="7"/>
+      <c r="D25" s="6"/>
       <c r="E25" t="s">
         <v>47</v>
       </c>
@@ -1537,10 +1540,10 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="7"/>
+      <c r="D26" s="6"/>
       <c r="E26" t="s">
         <v>48</v>
       </c>
@@ -1567,10 +1570,10 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="7"/>
+      <c r="D27" s="6"/>
       <c r="E27" t="s">
         <v>54</v>
       </c>
@@ -1597,10 +1600,10 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="7"/>
+      <c r="D28" s="6"/>
       <c r="E28" t="s">
         <v>48</v>
       </c>
@@ -1627,10 +1630,10 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="7"/>
+      <c r="D29" s="6"/>
       <c r="E29" t="s">
         <v>53</v>
       </c>
@@ -1657,16 +1660,16 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="9">
         <v>4700</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="7" t="s">
         <v>24</v>
       </c>
     </row>
